--- a/reports/二级子公司D_现金流量表_2026-10.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-10.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>75921300</v>
+        <v>73347869</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>704838888</v>
+        <v>684151080</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1514423</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>14587728</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>750109</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>7285834</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>378069</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3648605</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>300725</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2913470</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>226195</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2189387</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>150839</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1456884</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>112743</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1094369</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>75629</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>728778</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>187505</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1822900</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>95140</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>916221</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>59601</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>579229</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>194670</v>
+        <v>189796</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1883664</v>
+        <v>1830183</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1297800</v>
+        <v>1256052</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>12557760</v>
+        <v>12180763</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>77413770</v>
+        <v>78644695</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>49749000</v>
+        <v>48104023</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>481380800</v>
+        <v>467509053</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>504720</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>4860532</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>374857</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3644262</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>252340</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2431728</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>187635</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1821212</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>125919</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1216297</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>94553</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>915119</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7786800</v>
+        <v>7557033</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>75346560</v>
+        <v>73219543</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>4109700</v>
+        <v>3997830</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>39766240</v>
+        <v>38578701</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1622250</v>
+        <v>1569759</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>15697200</v>
+        <v>15247851</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>63267750</v>
+        <v>62768669</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>14146020</v>
+        <v>15876026</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>80056</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>824000</v>
+        <v>800820</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>698293</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>7210000</v>
+        <v>7005072</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>421556</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>4326000</v>
+        <v>4198112</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>778349</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>8039849</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>82400000</v>
+        <v>80016579</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1194169</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>12360000</v>
+        <v>11993751</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5523261</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>56650000</v>
+        <v>55042890</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>179742</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1854000</v>
+        <v>1801562</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8219591</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7441242</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1492501</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>15450000</v>
+        <v>14995293</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2490193</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>25750000</v>
+        <v>24978802</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2506821</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>25750000</v>
+        <v>25024858</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>79900</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>824000</v>
+        <v>799171</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4062594</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>2003868</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>20600000</v>
+        <v>19983934</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>1993392</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>20600000</v>
+        <v>20011035</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>321385</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3296000</v>
+        <v>3199222</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>281389</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2884000</v>
+        <v>2801167</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>39820</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>412000</v>
+        <v>399721</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2365073</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1697521</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>8295620</v>
+        <v>10132305</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>8295620</v>
+        <v>10132305</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
